--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_1/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_1/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4651</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9919</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7907</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7907</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_10', 'AU_11']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_32</t>
@@ -1233,7 +1245,6 @@
           <t>servicio business, servicio functional</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_31']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU22</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1385,14 +1391,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Typescript</t>
@@ -1416,13 +1419,11 @@
           <t>CF_M09_AU26</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_AU28</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1468,13 +1469,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>React</t>
@@ -1498,13 +1497,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1545,14 +1542,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Material UI</t>
@@ -1576,13 +1570,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_AU30</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1628,13 +1620,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1658,13 +1648,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1710,13 +1698,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -1740,13 +1726,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_AU13</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1792,13 +1776,11 @@
           <t>['AU_31']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -1817,14 +1799,11 @@
       <c r="P9" t="n">
         <v>55</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1865,14 +1844,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Shadcn</t>
@@ -1896,13 +1872,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU32</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1948,13 +1922,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Store</t>
@@ -1978,13 +1950,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU14</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2030,13 +2000,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2060,13 +2028,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2107,14 +2073,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>TypeORM</t>
@@ -2138,13 +2101,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_AU29</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2190,13 +2151,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2220,13 +2179,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2272,13 +2229,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2302,13 +2257,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_AU17</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2354,13 +2307,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2384,13 +2335,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2431,14 +2380,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>NextJS</t>
@@ -2462,13 +2408,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_AU31</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2509,14 +2453,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2540,13 +2481,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2587,14 +2526,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -2613,14 +2549,11 @@
       <c r="P19" t="n">
         <v>9</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2666,13 +2599,11 @@
           <t>['AU_05', 'AU_33']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2696,13 +2627,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2748,13 +2677,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>RDS</t>
@@ -2778,13 +2705,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2830,13 +2755,11 @@
           <t>['AU_32']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -2860,13 +2783,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2940,7 +2861,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Por un lado está el cliente, quien realiza las diferentes peticiones, y por otro lado está el servidor, quien las recibe y las procesas.</t>
@@ -2976,7 +2896,6 @@
           <t>Capa de presentación</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>En este caso, la capa de presentación es el cliente, es decir, el navegador web del usuario.</t>
@@ -3012,7 +2931,6 @@
           <t>Capa de negocio</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>En este caso, la capa de negocio es el servidor, es decir, el software que se encarga de procesar las peticiones del usuario.</t>
@@ -3048,7 +2966,6 @@
           <t>Capa de datos</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Capa de datos: Es la capa que se encarga de almacenar la información.</t>
@@ -3084,7 +3001,6 @@
           <t>Vista</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Es la parte encargada de mostrar la información al usuario.</t>
@@ -3120,7 +3036,6 @@
           <t>Acciones</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Son las acciones que puede realizar el usuario.</t>
@@ -3156,7 +3071,6 @@
           <t>Servicio business</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Se encarga de la gestión de usuarios, la autenticación y la autorización de los mismos.</t>
@@ -3192,7 +3106,6 @@
           <t>Servicio functional</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Este es el servicio que realiza toda la lógica importante de la plataforma.</t>
@@ -3228,7 +3141,6 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Todos los prototipos se han creado utilizando la herramienta Figma y permiten pensar y analizar de forma anticipada la interfaz de usuario.</t>
@@ -3264,7 +3176,6 @@
           <t>Swagger</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Los decoradores @ApiResponse son parte de Swagger [47] y permiten generar documentación de la API.</t>
@@ -3300,7 +3211,6 @@
           <t>SMPLRSpace</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>El primer paso para visualizar el mapa 3D es crear este mapa en la página web que ofrece la librería utilizada (SMPLRSpace).</t>
@@ -3331,7 +3241,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>capa de presentación, capa de negocio</t>
@@ -3367,7 +3276,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>servicio business, amazon dynamodb</t>
@@ -3408,7 +3316,6 @@
           <t>Cliente-Servidor</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>La plataforma de Waapiti es un servicio web, por tanto, como es habitual en este tipo de softwares, sigue la arquitectura cliente-servidor.</t>
@@ -3419,7 +3326,6 @@
           <t>CF_M09_AU07</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.8156</v>
       </c>
@@ -3440,7 +3346,6 @@
           <t>Arquitectura de 3 capas</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Para desacoplar las partes que componen el modelo de cliente-servidor, se ha utilizado la arquitectura de 3 capas.</t>
@@ -3476,7 +3381,6 @@
           <t>Patrón observador</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>El patrón observador es un patrón de diseño de software que define una dependencia de uno a muchos entre objetos, de forma que cuando un objeto cambia su estado, todos los objetos que dependen de él son notificados y actualizados automáticamente.</t>
@@ -3512,7 +3416,6 @@
           <t>Patrón provider</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>El patrón provider es un patrón de diseño de software que permite compartir información entre componentes de React sin necesidad de utilizar props.</t>
@@ -3548,7 +3451,6 @@
           <t>Patrón módulo</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Este es el patrón más importante dentro del lenguaje de JavaScript. Este patrón permite encapsular la información y exponer solo aquella que se desea compartir entre módulos (como funciones o componentes).</t>
@@ -3584,7 +3486,6 @@
           <t>Patrón gancho (hook)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Los ganchos son una nueva característica de React que permiten utilizar el estado y otras características de React sin necesidad de escribir una clase.</t>
@@ -3676,7 +3577,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player is an external device that allows content to be played on a non professional screen.</t>
@@ -3712,7 +3612,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -3743,7 +3642,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>client, waapiti platform</t>
@@ -3784,7 +3682,6 @@
           <t>Presentation layer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>This layer is responsible for displaying information to the user.</t>
@@ -3820,7 +3717,6 @@
           <t>Business layer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>This is the layer responsible for processing information.</t>
@@ -3856,7 +3752,6 @@
           <t>Data layer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>This is the layer responsible for storing information.</t>
@@ -3892,7 +3787,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>This is the part responsible for displaying information to the user.</t>
@@ -3928,7 +3822,6 @@
           <t>Actions</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>These are the actions that the user can perform.</t>
@@ -3959,7 +3852,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -3995,7 +3887,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -4036,7 +3927,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -4072,7 +3962,6 @@
           <t>Business layer (Backend)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
@@ -4108,7 +3997,6 @@
           <t>User Cache</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
@@ -4119,7 +4007,6 @@
           <t>AU_33</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>0.7455000000000001</v>
       </c>
@@ -4140,7 +4027,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4176,7 +4062,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4212,7 +4097,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -4248,7 +4132,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -4284,7 +4167,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -4315,7 +4197,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -4331,7 +4212,6 @@
           <t>AU_32</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.7227</v>
       </c>
@@ -4352,7 +4232,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -4388,7 +4267,6 @@
           <t>Client-Server Architecture</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
@@ -4424,7 +4302,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
@@ -4460,7 +4337,6 @@
           <t>Observer pattern</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
@@ -4496,7 +4372,6 @@
           <t>Provider pattern</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
@@ -4532,7 +4407,6 @@
           <t>Module Pattern</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>This is the most important pattern in the JavaScript language.</t>
@@ -4568,7 +4442,6 @@
           <t>Hook pattern</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
@@ -4604,7 +4477,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
